--- a/p_parameters/archive_parameters/codebooks/D3_coorte_con_bears.xlsx
+++ b/p_parameters/archive_parameters/codebooks/D3_coorte_con_bears.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="25">
   <si>
     <t xml:space="preserve">parameter</t>
   </si>
@@ -67,6 +67,9 @@
     <t xml:space="preserve">anticoag</t>
   </si>
   <si>
+    <t xml:space="preserve">digo</t>
+  </si>
+  <si>
     <t xml:space="preserve">med_anticol</t>
   </si>
   <si>
@@ -89,6 +92,9 @@
   </si>
   <si>
     <t xml:space="preserve">med_anticoag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">med_digo</t>
   </si>
 </sst>
 </file>
@@ -348,261 +354,258 @@
       <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="0"/>
-      <c r="D2" s="0"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="0"/>
-      <c r="D3" s="0"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="0"/>
-      <c r="D4" s="0"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="0"/>
-      <c r="D5" s="0"/>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="0"/>
-      <c r="D6" s="0"/>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="0"/>
-      <c r="D7" s="0"/>
-    </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B9" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="0"/>
-      <c r="D8" s="0"/>
-    </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="0"/>
-      <c r="D9" s="0"/>
-    </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="2" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="0"/>
-      <c r="D10" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="0" t="n">
-        <v>-365</v>
-      </c>
-      <c r="F10" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="0"/>
-      <c r="D11" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="0" t="n">
-        <v>-365</v>
-      </c>
-      <c r="F11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="1"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="0"/>
-      <c r="D12" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="D12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="0" t="n">
+      <c r="E12" s="1" t="n">
         <v>-365</v>
       </c>
-      <c r="F12" s="0" t="n">
+      <c r="F12" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="0"/>
-      <c r="D13" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="E13" s="1" t="n">
         <v>-365</v>
       </c>
-      <c r="F13" s="0" t="n">
+      <c r="F13" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="0"/>
-      <c r="D14" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1" t="n">
         <v>-365</v>
       </c>
-      <c r="F14" s="0" t="n">
+      <c r="F14" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="0"/>
-      <c r="D15" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="D15" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="0" t="n">
+      <c r="E15" s="1" t="n">
         <v>-365</v>
       </c>
-      <c r="F15" s="0" t="n">
+      <c r="F15" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>-365</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>-365</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="0"/>
-      <c r="D16" s="0" t="n">
+      <c r="B18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E16" s="0" t="n">
+      <c r="E18" s="1" t="n">
         <v>-365</v>
       </c>
-      <c r="F16" s="0" t="n">
+      <c r="F18" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="1"/>
-    </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="0"/>
-      <c r="D17" s="0" t="n">
+      <c r="B19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="0" t="n">
+      <c r="E19" s="1" t="n">
         <v>-365</v>
       </c>
-      <c r="F17" s="0" t="n">
+      <c r="F19" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0"/>
-      <c r="C18" s="0"/>
-      <c r="D18" s="0"/>
-    </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-    </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
+      <c r="A20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>-365</v>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5"/>

--- a/p_parameters/archive_parameters/codebooks/D3_coorte_con_bears.xlsx
+++ b/p_parameters/archive_parameters/codebooks/D3_coorte_con_bears.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="25">
   <si>
     <t xml:space="preserve">parameter</t>
   </si>
@@ -362,24 +362,12 @@
       </c>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -387,7 +375,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -395,7 +383,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -403,7 +391,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -411,7 +399,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -419,7 +407,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -427,15 +415,15 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>13</v>
+      <c r="B9" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -443,23 +431,32 @@
         <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>15</v>
+      <c r="A11" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>-365</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>1</v>
@@ -473,10 +470,10 @@
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>1</v>
@@ -490,10 +487,10 @@
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>1</v>
@@ -507,13 +504,13 @@
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>-365</v>
@@ -524,13 +521,13 @@
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>-365</v>
@@ -541,13 +538,13 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>-365</v>
@@ -557,14 +554,14 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
-        <v>13</v>
+      <c r="A18" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>-365</v>
@@ -575,10 +572,10 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>1</v>
@@ -591,21 +588,11 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>-365</v>
-      </c>
-      <c r="F20" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5"/>
@@ -616,27 +603,26 @@
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
       <c r="D22" s="6"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5"/>
       <c r="D23" s="6"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="8"/>
       <c r="D24" s="6"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7"/>
-      <c r="B25" s="8"/>
       <c r="D25" s="6"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
@@ -649,6 +635,7 @@
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7"/>
+      <c r="B27" s="9"/>
       <c r="D27" s="6"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
@@ -659,14 +646,13 @@
       <c r="D28" s="6"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7"/>
-      <c r="B29" s="9"/>
+      <c r="A29" s="5"/>
       <c r="D29" s="6"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5"/>
@@ -700,19 +686,19 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5"/>
-      <c r="D35" s="6"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5"/>
+      <c r="B36" s="6"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5"/>
-      <c r="B37" s="6"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
@@ -748,18 +734,13 @@
       <c r="G42" s="1"/>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="5"/>
+      <c r="A43" s="10"/>
+      <c r="B43" s="10"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
     </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="10"/>
-      <c r="B44" s="10"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-    </row>
+    <row r="1048552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
